--- a/data/file_generation/input/data_79/辞工汇总表2024年度.xlsx
+++ b/data/file_generation/input/data_79/辞工汇总表2024年度.xlsx
@@ -5057,26 +5057,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C423C3C-5386-4516-9529-CF46531B9816}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F77C2DE-24C2-47B0-A260-F4811EAAEF81}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7C7E154-FEEA-4FF3-806E-085C2F2F04C6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47CA8F43-D394-49DC-AC8E-E4DAFC160F2E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{377BEDB7-0CB8-47EC-8527-C8F832570373}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD6E4B59-3427-4CD6-BC6C-34B478AF91D0}"/>
 </file>